--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92230</v>
+        <v>92232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92232</v>
+        <v>92238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92238</v>
+        <v>92241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92241</v>
+        <v>92258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92258</v>
+        <v>92263</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123325161</v>
       </c>
       <c r="B2" t="n">
-        <v>92263</v>
+        <v>92265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123325161</v>
+        <v>123325159</v>
       </c>
       <c r="B2" t="n">
-        <v>92265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601358</v>
+        <v>601353</v>
       </c>
       <c r="R2" t="n">
-        <v>6917832</v>
+        <v>6917834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1796</t>
+          <t>2024_1798</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,6 +793,131 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123325161</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kalberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>601358</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6917832</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_1796</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ofir Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 9200-2022 artfynd.xlsx
+++ b/artfynd/A 9200-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,8 +932,17 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123325161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>